--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>101353</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404748.6580926224</v>
+        <v>404749</v>
       </c>
       <c r="R2" t="n">
-        <v>6332332.912380742</v>
+        <v>6332333</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404747.1551258233</v>
+        <v>404747</v>
       </c>
       <c r="R3" t="n">
-        <v>6332432.860082982</v>
+        <v>6332433</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404748.6580926224</v>
+        <v>404749</v>
       </c>
       <c r="R4" t="n">
-        <v>6332332.912380742</v>
+        <v>6332333</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103702</v>
+        <v>103710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99339</v>
+        <v>99344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103710</v>
+        <v>103712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103712</v>
+        <v>103739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99345</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103739</v>
+        <v>103745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103745</v>
+        <v>103752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103752</v>
+        <v>103756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99385</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103756</v>
+        <v>103763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103766</v>
+        <v>103771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99399</v>
+        <v>99404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103771</v>
+        <v>103779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99404</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74196678</v>
       </c>
       <c r="B2" t="n">
-        <v>103779</v>
+        <v>103789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269464</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74602441</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74602441</v>
+        <v>74500472</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,23 +908,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,7 +968,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Lycopodium annotinum. LEG: Göran Wendt, Vera Wendt, Börje Wennberg</t>
+          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Huperzia selago. LEG: Göran Wendt, Vera Wendt, Börje Wennberg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +982,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bokskog</t>
+          <t>Skogsslänt mot kärr</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1001,6 +997,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74602441</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97540</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L24 Brunnsgård 150 m OSO, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>404749</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6332333</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Villstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1987-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Lycopodium annotinum. LEG: Göran Wendt, Vera Wendt, Börje Wennberg</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -675,38 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74196678</v>
+        <v>74500472</v>
       </c>
       <c r="B2" t="n">
-        <v>103789</v>
+        <v>97977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222075</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk dunört</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epilobium obscurum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bokelund 150 m O, Sm</t>
+          <t>L24 Brunnsgård 150 m OSO, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -740,7 +736,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -750,7 +746,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Epilobium obscurum. LEG: Göran Wendt, Vera Wendt, Börje Wennberg. KOM: Det. ThK</t>
+          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Huperzia selago. LEG: Göran Wendt, Vera Wendt, Börje Wennberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +760,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bete</t>
+          <t>Skogsslänt mot kärr</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74269464</v>
+        <v>74602441</v>
       </c>
       <c r="B3" t="n">
-        <v>99422</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222361</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bokelund västra huset 250 m NO, Sm</t>
+          <t>L24 Brunnsgård 150 m OSO, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404747</v>
+        <v>404749</v>
       </c>
       <c r="R3" t="n">
-        <v>6332433</v>
+        <v>6332333</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -856,12 +852,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D7b 0709. SOM: Carex pulicaris. LEG: Göran Wendt</t>
+          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Lycopodium annotinum. LEG: Göran Wendt, Vera Wendt, Börje Wennberg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +871,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kärr</t>
+          <t>Bokskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,34 +893,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74500472</v>
+        <v>74196678</v>
       </c>
       <c r="B4" t="n">
-        <v>97534</v>
+        <v>104282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>222075</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Mörk dunört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Epilobium obscurum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>L24 Brunnsgård 150 m OSO, Sm</t>
+          <t>Bokelund 150 m O, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Huperzia selago. LEG: Göran Wendt, Vera Wendt, Börje Wennberg</t>
+          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Epilobium obscurum. LEG: Göran Wendt, Vera Wendt, Börje Wennberg. KOM: Det. ThK</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,7 +982,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsslänt mot kärr</t>
+          <t>Bete</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,27 +1004,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74602441</v>
+        <v>74269464</v>
       </c>
       <c r="B5" t="n">
-        <v>97540</v>
+        <v>99878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>222361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1035,14 +1035,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>L24 Brunnsgård 150 m OSO, Sm</t>
+          <t>Bokelund västra huset 250 m NO, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404749</v>
+        <v>404747</v>
       </c>
       <c r="R5" t="n">
-        <v>6332333</v>
+        <v>6332433</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
+          <t>1987-12-31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D7b 0609. SOM: Lycopodium annotinum. LEG: Göran Wendt, Vera Wendt, Börje Wennberg</t>
+          <t>Smålands flora 2007: KOO: 5D7b 0709. SOM: Carex pulicaris. LEG: Göran Wendt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bokskog</t>
+          <t>Kärr</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 19576-2025 artfynd.xlsx
+++ b/artfynd/A 19576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74500472</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74602441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74196678</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74269464</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>